--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487443_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487443_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1657</v>
+        <v>6.1252</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8611</v>
+        <v>6.1681</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3046</v>
+        <v>-0.0429</v>
       </c>
       <c r="G2" t="n">
         <v>6.4371</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3521</v>
+        <v>-1.3926</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0516</v>
+        <v>-0.7446</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3005</v>
+        <v>-0.648</v>
       </c>
       <c r="V2" t="n">
         <v>0.4931</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5252</v>
+        <v>3.344</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0439</v>
+        <v>1.1033</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4813</v>
+        <v>2.2408</v>
       </c>
       <c r="G3" t="n">
         <v>1.2519</v>
@@ -688,13 +688,13 @@
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2727</v>
+        <v>-0.4539</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7258</v>
+        <v>-0.6664</v>
       </c>
       <c r="U3" t="n">
-        <v>0.453</v>
+        <v>0.2125</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0039</v>
+        <v>3.1513</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9426</v>
+        <v>3.6356</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9387</v>
+        <v>-0.4843</v>
       </c>
       <c r="G4" t="n">
         <v>2.4345</v>
@@ -766,13 +766,13 @@
         <v>2.3502</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7808</v>
+        <v>-1.6334</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3694</v>
+        <v>-0.6764</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.4115</v>
+        <v>-0.957</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9773</v>
+        <v>2.9381</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4919</v>
+        <v>-0.0231</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4691</v>
+        <v>2.9613</v>
       </c>
       <c r="G5" t="n">
         <v>1.6575</v>
@@ -844,13 +844,13 @@
         <v>2.546</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6756</v>
+        <v>-0.7147</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9745</v>
+        <v>-0.5058</v>
       </c>
       <c r="U5" t="n">
-        <v>0.299</v>
+        <v>-0.2089</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5507</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2898</v>
+        <v>2.1934</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2267</v>
+        <v>1.1837</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0632</v>
+        <v>1.0097</v>
       </c>
       <c r="G6" t="n">
         <v>1.3994</v>
@@ -922,13 +922,13 @@
         <v>2.3502</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7179</v>
+        <v>-0.8143</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4882</v>
+        <v>-0.5311</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2297</v>
+        <v>-0.2832</v>
       </c>
       <c r="V6" t="n">
         <v>1.2166</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3913</v>
+        <v>0.5204</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1383</v>
+        <v>-0.1116</v>
       </c>
       <c r="G7" t="n">
         <v>0.2371</v>
@@ -1000,13 +1000,13 @@
         <v>0.5875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4333</v>
+        <v>-0.3042</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2551</v>
+        <v>-0.2283</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. CAAMAÑO ARAGUNDE</t>
+          <t>R. SANTORUM OTERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4982</v>
+        <v>-0.3973</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7806</v>
+        <v>0.484</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2824</v>
+        <v>-0.8813</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5931</v>
+        <v>0.6842</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7295</v>
+        <v>0.0579</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1364</v>
+        <v>0.6262</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6618000000000001</v>
+        <v>1.7591</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6618000000000001</v>
+        <v>1.1432</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6159</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0687</v>
+        <v>-1.075</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0677</v>
+        <v>-1.0853</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1364</v>
+        <v>0.0104</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.101</v>
+        <v>-0.4732</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1188</v>
+        <v>-0.2958</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0178</v>
+        <v>-0.1773</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SANTORUM OTERO</t>
+          <t>C. CAAMAÑO ARAGUNDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8263</v>
+        <v>-0.4715</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3223</v>
+        <v>-0.7806</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1486</v>
+        <v>0.3091</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6842</v>
+        <v>-0.5931</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0579</v>
+        <v>-0.7295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6262</v>
+        <v>0.1364</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7591</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1432</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6159</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.075</v>
+        <v>0.0687</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0853</v>
+        <v>-0.0677</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0104</v>
+        <v>0.1364</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9022</v>
+        <v>-0.0743</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4576</v>
+        <v>-0.1188</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4446</v>
+        <v>0.0446</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6432</v>
+        <v>-3.3805</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8746</v>
+        <v>-4.7723</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2314</v>
+        <v>1.3918</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3551</v>
@@ -1234,13 +1234,13 @@
         <v>2.3502</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6798</v>
+        <v>-1.4171</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6664</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0135</v>
+        <v>-0.8531</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ FERNANDEZ</t>
+          <t>D. REY MARIÑO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8515</v>
+        <v>-3.6943</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0728</v>
+        <v>-2.1686</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2213</v>
+        <v>-1.5256</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8095</v>
+        <v>-2.9588</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2229</v>
+        <v>-2.4186</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5866</v>
+        <v>-0.5402</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.3678</v>
+        <v>-1.8234</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.3615</v>
+        <v>-1.9446</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0063</v>
+        <v>0.1212</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5583</v>
+        <v>-1.1354</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1385</v>
+        <v>-0.4739</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4197</v>
+        <v>-0.6615</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>0.996</v>
+        <v>-0.8103</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2327</v>
+        <v>-0.3452</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2367</v>
+        <v>-0.4651</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3329</v>
+        <v>-1.492</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3329</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. REY MARIÑO</t>
+          <t>A. RODRIGUEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1838</v>
+        <v>-4.6818</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.578</v>
+        <v>-7.0367</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6058</v>
+        <v>2.3549</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9588</v>
+        <v>-3.8095</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4186</v>
+        <v>-2.2229</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5402</v>
+        <v>-1.5866</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8234</v>
+        <v>-4.3678</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9446</v>
+        <v>-2.3615</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1212</v>
+        <v>-2.0063</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1354</v>
+        <v>0.5583</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4739</v>
+        <v>0.1385</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6615</v>
+        <v>0.4197</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5668</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R12" t="n">
         <v>1.5668</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2998</v>
+        <v>0.1657</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7546</v>
+        <v>0.2688</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5453</v>
+        <v>-0.1031</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.492</v>
+        <v>0.3329</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.492</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.350199999999997</v>
+        <v>5.647000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.871599999999999</v>
+        <v>-1.5746</v>
       </c>
       <c r="F13" t="n">
         <v>7.2219</v>
@@ -1438,13 +1438,13 @@
         <v>-1.0207</v>
       </c>
       <c r="I13" t="n">
-        <v>5.405899999999999</v>
+        <v>5.4059</v>
       </c>
       <c r="J13" t="n">
         <v>9.604200000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>5.744300000000002</v>
+        <v>5.744300000000003</v>
       </c>
       <c r="L13" t="n">
         <v>3.8597</v>
@@ -1453,7 +1453,7 @@
         <v>-5.218999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.7652</v>
+        <v>-6.765199999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1.5461</v>
@@ -1468,13 +1468,13 @@
         <v>19.5847</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.219199999999999</v>
+        <v>-7.922299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.552400000000001</v>
+        <v>-4.2552</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.6671</v>
+        <v>-3.6669</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6084000000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.5899</v>
+        <v>6.2492</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9402</v>
+        <v>6.4355</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6498</v>
+        <v>-0.1864</v>
       </c>
       <c r="G14" t="n">
-        <v>4.077</v>
+        <v>3.967</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3039</v>
+        <v>2.5121</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7731</v>
+        <v>1.4549</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5063</v>
+        <v>6.5722</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8904</v>
+        <v>3.5266</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6159</v>
+        <v>3.0456</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5707</v>
+        <v>-2.6052</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4135</v>
+        <v>-1.0145</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1572</v>
+        <v>-1.5906</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7834</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1543</v>
+        <v>-1.9585</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8044</v>
+        <v>2.0448</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0963</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7081</v>
+        <v>1.382</v>
       </c>
       <c r="V14" t="n">
-        <v>1.492</v>
+        <v>1.2166</v>
       </c>
       <c r="W14" t="n">
-        <v>1.492</v>
+        <v>1.159</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.4251</v>
+        <v>5.9474</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0262</v>
+        <v>3.4285</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3989</v>
+        <v>2.5189</v>
       </c>
       <c r="G15" t="n">
-        <v>3.967</v>
+        <v>4.077</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5121</v>
+        <v>3.3039</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4549</v>
+        <v>0.7731</v>
       </c>
       <c r="J15" t="n">
-        <v>6.5722</v>
+        <v>3.5063</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5266</v>
+        <v>2.8904</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0456</v>
+        <v>0.6159</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.6052</v>
+        <v>0.5707</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0145</v>
+        <v>0.4135</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5906</v>
+        <v>0.1572</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9792</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9585</v>
+        <v>-2.1543</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2207</v>
+        <v>1.1619</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2535</v>
+        <v>0.5846</v>
       </c>
       <c r="U15" t="n">
-        <v>1.9673</v>
+        <v>0.5773</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2166</v>
+        <v>1.492</v>
       </c>
       <c r="W15" t="n">
-        <v>1.159</v>
+        <v>1.492</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. SAMA PEREZ</t>
+          <t>D. VILLADONIGA AMADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0585</v>
+        <v>-0.4101</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.1132</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4944</v>
+        <v>-0.5232</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7181</v>
+        <v>1.3701</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7423999999999999</v>
+        <v>-0.1612</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4605</v>
+        <v>1.5313</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1641</v>
+        <v>2.1618</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3017</v>
+        <v>0.7876</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1376</v>
+        <v>1.3741</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8822</v>
+        <v>-0.7917</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5593</v>
+        <v>-0.9489</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3229</v>
+        <v>0.1572</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.1336</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.1128</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0265</v>
+        <v>0.8857</v>
       </c>
       <c r="T16" t="n">
-        <v>1.618</v>
+        <v>0.5758</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4085</v>
+        <v>0.31</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8837</v>
+        <v>-1.8825</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8837</v>
+        <v>-0.6659</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>I. SAMA PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4153</v>
+        <v>-0.5038</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.8055</v>
+        <v>0.0412</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3902</v>
+        <v>-0.5451</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2858</v>
+        <v>-0.7181</v>
       </c>
       <c r="H17" t="n">
-        <v>1.559</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2733</v>
+        <v>-1.4605</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0234</v>
+        <v>2.1641</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9424</v>
+        <v>2.3017</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9659</v>
+        <v>-0.1376</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3092</v>
+        <v>-2.8822</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6166</v>
+        <v>-1.5593</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6926</v>
+        <v>-1.3229</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9585</v>
+        <v>-3.1336</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1336</v>
+        <v>-4.1128</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2574</v>
+        <v>2.4641</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3515</v>
+        <v>1.1063</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.09420000000000001</v>
+        <v>1.3579</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. VILLADONIGA AMADO</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7558</v>
+        <v>-0.5454</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0108</v>
+        <v>-3.4195</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7665999999999999</v>
+        <v>2.8741</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3701</v>
+        <v>0.2858</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1612</v>
+        <v>1.559</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5313</v>
+        <v>-1.2733</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1618</v>
+        <v>-1.0234</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7876</v>
+        <v>0.9424</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3741</v>
+        <v>-1.9659</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7917</v>
+        <v>1.3092</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9489</v>
+        <v>0.6166</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1572</v>
+        <v>0.6926</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7834</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-3.1336</v>
       </c>
       <c r="R18" t="n">
         <v>1.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>0.54</v>
+        <v>1.1273</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4734</v>
+        <v>0.7375</v>
       </c>
       <c r="U18" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.3898</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8825</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0759</v>
+        <v>-0.7837</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6801</v>
+        <v>-1.5777</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6041</v>
+        <v>0.794</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0497</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5343</v>
+        <v>-0.242</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3564</v>
+        <v>-0.2541</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1779</v>
+        <v>0.0121</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2754</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8229</v>
+        <v>-1.4505</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0933</v>
+        <v>-0.991</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7296</v>
+        <v>-0.4595</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6181</v>
@@ -2014,13 +2014,13 @@
         <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6172</v>
+        <v>-0.2448</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.297</v>
+        <v>-0.1947</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3202</v>
+        <v>-0.0501</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. HERMIDA PEREZ</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2095</v>
+        <v>-2.6087</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0177</v>
+        <v>-4.0525</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1918</v>
+        <v>1.4438</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1804</v>
+        <v>-2.935</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6847</v>
+        <v>-1.6213</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4957</v>
+        <v>-1.3137</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0367</v>
+        <v>-3.2891</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3285</v>
+        <v>-1.965</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-1.3241</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1437</v>
+        <v>0.3541</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3562</v>
+        <v>0.3437</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7875</v>
+        <v>0.0104</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1543</v>
+        <v>-0.1958</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4213</v>
+        <v>-0.653</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1733</v>
+        <v>-0.5676</v>
       </c>
       <c r="U21" t="n">
-        <v>1.248</v>
+        <v>-0.0854</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>A. HERMIDA PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1904</v>
+        <v>-2.7719</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2572</v>
+        <v>-2.5294</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0667</v>
+        <v>-0.2425</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.935</v>
+        <v>-3.1804</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6213</v>
+        <v>-1.6847</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3137</v>
+        <v>-1.4957</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.2891</v>
+        <v>-1.0367</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.965</v>
+        <v>-0.3285</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3241</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3541</v>
+        <v>-2.1437</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3437</v>
+        <v>-1.3562</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0104</v>
+        <v>-0.7875</v>
       </c>
       <c r="P22" t="n">
+        <v>-1.1751</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-2.1543</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.9792</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-0.1958</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.1751</v>
-      </c>
       <c r="S22" t="n">
-        <v>-1.2347</v>
+        <v>1.8589</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7722</v>
+        <v>0.6616</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4624</v>
+        <v>1.1973</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.953799999999999</v>
+        <v>-7.1082</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.8982</v>
+        <v>-4.6702</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0556</v>
+        <v>-2.438</v>
       </c>
       <c r="G23" t="n">
         <v>-5.5838</v>
@@ -2248,13 +2248,13 @@
         <v>0.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6649</v>
+        <v>1.1807</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8734</v>
+        <v>0.3546</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2084</v>
+        <v>0.826</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5507</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.350099999999999</v>
+        <v>-3.985699999999999</v>
       </c>
       <c r="E24" t="n">
         <v>-7.2219</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8717</v>
+        <v>3.2361</v>
       </c>
       <c r="G24" t="n">
         <v>-4.385199999999999</v>
@@ -2299,7 +2299,7 @@
         <v>-5.406000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>5.219100000000003</v>
+        <v>5.219099999999999</v>
       </c>
       <c r="K24" t="n">
         <v>6.7651</v>
@@ -2314,7 +2314,7 @@
         <v>-5.7446</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.859699999999999</v>
+        <v>-3.8597</v>
       </c>
       <c r="P24" t="n">
         <v>-9.792400000000001</v>
@@ -2326,13 +2326,13 @@
         <v>9.792300000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>8.219200000000001</v>
+        <v>9.583599999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>3.667</v>
+        <v>3.6668</v>
       </c>
       <c r="U24" t="n">
-        <v>4.552200000000001</v>
+        <v>5.9169</v>
       </c>
       <c r="V24" t="n">
         <v>0.6082999999999998</v>
@@ -2341,7 +2341,7 @@
         <v>3.4771</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.8688</v>
+        <v>-2.868799999999999</v>
       </c>
     </row>
   </sheetData>
